--- a/files/samples/2026-10/신OO님_보장분석_제안보고서_20260814_1_m0bs3.xlsx
+++ b/files/samples/2026-10/신OO님_보장분석_제안보고서_20260814_1_m0bs3.xlsx
@@ -2244,7 +2244,7 @@
     <t>1,000만</t>
   </si>
   <si>
-    <t>피플라이프 성공금융 조진열</t>
+    <t>OOO</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
